--- a/output/pdf_financials_xlsx/TORQ.xlsx
+++ b/output/pdf_financials_xlsx/TORQ.xlsx
@@ -1267,34 +1267,34 @@
         <v>-2.10874</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.862316</v>
+        <v>0</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.021326</v>
+        <v>0.258876</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>32.580737</v>
+        <v>0.005223</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.508939</v>
+        <v>0.001377</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.265774</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>6.478104</v>
@@ -1303,13 +1303,13 @@
         <v>11.878804</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>19.21164</v>
+        <v>-19.21164</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>15.760546</v>
+        <v>-15.760546</v>
       </c>
     </row>
     <row r="17">
@@ -1355,10 +1355,10 @@
         <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-12.956208</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.159458</v>
+        <v>-23.59815</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -1567,49 +1567,49 @@
         <v>-2.10874</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.431158</v>
+        <v>-0.431158</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.381225</v>
+        <v>-1.381225</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>16.287757</v>
+        <v>-16.287757</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.253781</v>
+        <v>-0.253781</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.132887</v>
+        <v>-0.132887</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>6.478104</v>
+        <v>-6.478104</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>11.719346</v>
+        <v>-11.719346</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>19.21164</v>
+        <v>-19.21164</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>15.760546</v>
+        <v>-15.760546</v>
       </c>
     </row>
     <row r="21">
@@ -1741,49 +1741,49 @@
         <v>-2.10874</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.431158</v>
+        <v>-0.431158</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.381225</v>
+        <v>-1.381225</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>16.287757</v>
+        <v>-16.287757</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.253781</v>
+        <v>-0.253781</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.132887</v>
+        <v>-0.132887</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>6.478104</v>
+        <v>-6.478104</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>11.719346</v>
+        <v>-11.719346</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.21164</v>
+        <v>-19.21164</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>15.760546</v>
+        <v>-15.760546</v>
       </c>
     </row>
     <row r="24">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>7.185967</v>
+        <v>-7.185967</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>17.265312</v>
+        <v>-17.265312</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>34.654802</v>
+        <v>-34.654802</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1951,31 +1951,31 @@
         </is>
       </c>
       <c r="J26" s="3" t="n">
-        <v>33.02495</v>
+        <v>-33.02495</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>73.992</v>
+        <v>-73.992</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>81.22595</v>
+        <v>-81.22595</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>83.88679999999999</v>
+        <v>-83.88679999999999</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>80.97629999999999</v>
+        <v>-80.97629999999999</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>90.148815</v>
+        <v>-90.148815</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>106.731333</v>
+        <v>-106.731333</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>137.936933</v>
+        <v>-137.936933</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>175.117178</v>
+        <v>-175.117178</v>
       </c>
     </row>
     <row r="27">
@@ -1991,34 +1991,34 @@
         <v>-2.10874</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.862316</v>
+        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.021326</v>
+        <v>0.258876</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>32.580737</v>
+        <v>0.005223</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.508939</v>
+        <v>0.001377</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.265774</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>6.478104</v>
@@ -2027,13 +2027,13 @@
         <v>11.878804</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>19.21164</v>
+        <v>-19.21164</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>15.760546</v>
+        <v>-15.760546</v>
       </c>
     </row>
     <row r="28">
@@ -2107,34 +2107,34 @@
         <v>-2.10874</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.866408</v>
+        <v>0.004092</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.022056</v>
+        <v>0.259606</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>32.580737</v>
+        <v>0.005223</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.508939</v>
+        <v>0.001377</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.265774</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6.478104</v>
@@ -2143,13 +2143,13 @@
         <v>12.060454</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.494514</v>
+        <v>-18.928766</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>12.493001</v>
+        <v>-12.335647</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>15.762846</v>
+        <v>-15.758246</v>
       </c>
     </row>
     <row r="30">
@@ -2256,50 +2256,54 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>50</v>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>54.28414543812882</v>
+        <v>633.5469491184969</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>50.00801547245539</v>
+        <v>311946.7738847405</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>50.1352814384435</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>50</v>
+        <v>18529.99273783587</v>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1.342374198614608</v>
+        <v>198.6576258013854</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5919,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.547271</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>13.890761</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>14.297803</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>16.202228</v>
       </c>
     </row>
     <row r="93">
@@ -7359,13 +7363,13 @@
         <v>-0.240174</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.325334</v>
+        <v>-0.010035</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.2517</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -10066,7 +10070,11 @@
           <t>Stock options and warrants reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -12092,7 +12100,11 @@
           <t>Stock options and warrants reserve</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -13007,7 +13019,11 @@
           <t>Stock options and warrants reserve</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -43256,7 +43272,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -45492,7 +45512,11 @@
           <t>Exploration and evaluation expenditures (note 7)</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E371" t="inlineStr">
         <is>
           <t>-</t>
@@ -58945,10 +58969,10 @@
         </is>
       </c>
       <c r="T503" s="5" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="U503" s="5" t="n">
-        <v>15.760546</v>
+        <v>-15.760546</v>
       </c>
     </row>
     <row r="504">
@@ -61337,13 +61361,13 @@
         </is>
       </c>
       <c r="R527" s="5" t="n">
-        <v>11.719346</v>
+        <v>-11.719346</v>
       </c>
       <c r="S527" s="5" t="n">
-        <v>19.21164</v>
+        <v>-19.21164</v>
       </c>
       <c r="T527" s="5" t="n">
-        <v>12.414324</v>
+        <v>-12.414324</v>
       </c>
       <c r="U527" t="inlineStr">
         <is>
@@ -61542,10 +61566,10 @@
         </is>
       </c>
       <c r="S529" s="5" t="n">
-        <v>19.269891</v>
+        <v>-19.269891</v>
       </c>
       <c r="T529" s="5" t="n">
-        <v>12.247724</v>
+        <v>-12.247724</v>
       </c>
       <c r="U529" t="inlineStr">
         <is>
@@ -62945,10 +62969,10 @@
         </is>
       </c>
       <c r="R543" s="5" t="n">
-        <v>11.577306</v>
+        <v>-11.577306</v>
       </c>
       <c r="S543" s="5" t="n">
-        <v>19.269891</v>
+        <v>-19.269891</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -64433,10 +64457,10 @@
         </is>
       </c>
       <c r="Q558" s="5" t="n">
-        <v>6.478104</v>
+        <v>-6.478104</v>
       </c>
       <c r="R558" s="5" t="n">
-        <v>11.719346</v>
+        <v>-11.719346</v>
       </c>
       <c r="S558" t="inlineStr">
         <is>
@@ -64635,10 +64659,10 @@
         </is>
       </c>
       <c r="Q560" s="5" t="n">
-        <v>6.52902</v>
+        <v>-6.52902</v>
       </c>
       <c r="R560" s="5" t="n">
-        <v>11.577306</v>
+        <v>-11.577306</v>
       </c>
       <c r="S560" t="inlineStr">
         <is>
@@ -65903,19 +65927,19 @@
         </is>
       </c>
       <c r="L573" s="5" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="M573" s="5" t="n">
-        <v>0.6604989999999999</v>
+        <v>-0.6604989999999999</v>
       </c>
       <c r="N573" s="5" t="n">
-        <v>4.43952</v>
+        <v>-4.43952</v>
       </c>
       <c r="O573" s="5" t="n">
-        <v>4.873557</v>
+        <v>-4.873557</v>
       </c>
       <c r="P573" s="5" t="n">
-        <v>1.677736</v>
+        <v>-1.677736</v>
       </c>
       <c r="Q573" t="inlineStr">
         <is>
@@ -66213,10 +66237,10 @@
         </is>
       </c>
       <c r="O576" s="5" t="n">
-        <v>4.873033</v>
+        <v>-4.873033</v>
       </c>
       <c r="P576" s="5" t="n">
-        <v>1.673966</v>
+        <v>-1.673966</v>
       </c>
       <c r="Q576" t="inlineStr">
         <is>
@@ -67001,10 +67025,10 @@
         </is>
       </c>
       <c r="M584" s="5" t="n">
-        <v>0.001024</v>
+        <v>-0.001024</v>
       </c>
       <c r="N584" s="5" t="n">
-        <v>0.003289</v>
+        <v>-0.003289</v>
       </c>
       <c r="O584" s="5" t="n">
         <v>-0.0005240000000000001</v>
@@ -67097,16 +67121,16 @@
         </is>
       </c>
       <c r="L585" s="5" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="M585" s="5" t="n">
-        <v>0.661523</v>
+        <v>-0.661523</v>
       </c>
       <c r="N585" s="5" t="n">
-        <v>4.442809</v>
+        <v>-4.442809</v>
       </c>
       <c r="O585" s="5" t="n">
-        <v>4.873033</v>
+        <v>-4.873033</v>
       </c>
       <c r="P585" t="inlineStr">
         <is>
@@ -69674,10 +69698,10 @@
         </is>
       </c>
       <c r="K611" s="5" t="n">
-        <v>0.132887</v>
+        <v>-0.132887</v>
       </c>
       <c r="L611" s="5" t="n">
-        <v>0.460357</v>
+        <v>-0.460357</v>
       </c>
       <c r="M611" t="inlineStr">
         <is>
@@ -71071,10 +71095,10 @@
         </is>
       </c>
       <c r="J625" s="5" t="n">
-        <v>0.253781</v>
+        <v>-0.253781</v>
       </c>
       <c r="K625" s="5" t="n">
-        <v>0.132887</v>
+        <v>-0.132887</v>
       </c>
       <c r="L625" t="inlineStr">
         <is>
@@ -71975,10 +71999,10 @@
         </is>
       </c>
       <c r="I634" s="5" t="n">
-        <v>16.287757</v>
+        <v>-16.287757</v>
       </c>
       <c r="J634" s="5" t="n">
-        <v>0.253781</v>
+        <v>-0.253781</v>
       </c>
       <c r="K634" t="inlineStr">
         <is>
@@ -73180,10 +73204,10 @@
         </is>
       </c>
       <c r="H646" s="5" t="n">
-        <v>1.381225</v>
+        <v>-1.381225</v>
       </c>
       <c r="I646" s="5" t="n">
-        <v>16.287757</v>
+        <v>-16.287757</v>
       </c>
       <c r="J646" t="inlineStr">
         <is>
@@ -74399,10 +74423,10 @@
         </is>
       </c>
       <c r="G658" s="5" t="n">
-        <v>0.431158</v>
+        <v>-0.431158</v>
       </c>
       <c r="H658" s="5" t="n">
-        <v>1.381225</v>
+        <v>-1.381225</v>
       </c>
       <c r="I658" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/TORQ.xlsx
+++ b/output/pdf_financials_xlsx/TORQ.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.043751</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012585</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1053,31 +1053,31 @@
         <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010872</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.146577</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.280861</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.245363</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.195681</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.374638</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.063538</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.030816</v>
       </c>
     </row>
     <row r="13">
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.050313</v>
+        <v>-4.006562</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-2.10874</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.258876</v>
+        <v>0.271461</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.005223</v>
@@ -2009,31 +2009,31 @@
         <v>-0.460357</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.6604989999999999</v>
+        <v>-0.649627</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-4.43952</v>
+        <v>-4.292943</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.873557</v>
+        <v>-4.592696</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.677736</v>
+        <v>-1.432373</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>6.478104</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>11.878804</v>
+        <v>12.074485</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-19.21164</v>
+        <v>-18.837002</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-12.414324</v>
+        <v>-12.350786</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-15.760546</v>
+        <v>-15.72973</v>
       </c>
     </row>
     <row r="28">
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.050313</v>
+        <v>-4.006562</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-2.10874</v>
@@ -2110,7 +2110,7 @@
         <v>0.004092</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.259606</v>
+        <v>0.272191</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.005223</v>
@@ -2125,31 +2125,31 @@
         <v>-0.460357</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.6604989999999999</v>
+        <v>-0.649627</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-4.43952</v>
+        <v>-4.292943</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.873557</v>
+        <v>-4.592696</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.677736</v>
+        <v>-1.432373</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6.478104</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>12.060454</v>
+        <v>12.256135</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-18.928766</v>
+        <v>-18.554128</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-12.335647</v>
+        <v>-12.272109</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-15.758246</v>
+        <v>-15.72743</v>
       </c>
     </row>
     <row r="30">
@@ -2427,13 +2427,13 @@
         <v>0.370823</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.297266</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.34944</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.215521</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>5.864033</v>
@@ -2448,16 +2448,16 @@
         <v>10.838021</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.899324</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>12.470543</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.48797</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.538284</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -2543,13 +2543,13 @@
         <v>0.370823</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.297266</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.34944</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.215521</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.864033</v>
@@ -2564,16 +2564,16 @@
         <v>10.838021</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.899324</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>12.470543</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.48797</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.538284</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3239,13 +3239,13 @@
         <v>0.258639</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.360405</v>
+        <v>0.063139</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.356319</v>
+        <v>0.006879</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.222421</v>
+        <v>0.0069</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.291365</v>
@@ -3260,16 +3260,16 @@
         <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.563757</v>
+        <v>0.6644330000000001</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>12.936637</v>
+        <v>0.466094</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.047003</v>
+        <v>0.559033</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.660507</v>
+        <v>0.122223</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>2.534636</v>
@@ -10892,7 +10892,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -13536,7 +13536,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -58395,7 +58395,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -58498,7 +58498,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -60991,7 +60991,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -62498,7 +62498,7 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -63896,7 +63896,7 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -73999,7 +73999,7 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
@@ -75326,7 +75326,7 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E667" s="5" t="n">

--- a/output/pdf_financials_xlsx/TORQ.xlsx
+++ b/output/pdf_financials_xlsx/TORQ.xlsx
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.837</v>
+        <v>-0.837</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1358,7 +1358,7 @@
         <v>-12.956208</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-23.59815</v>
+        <v>0.159458</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -2294,7 +2294,7 @@
         <v>200</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>198.6576258013854</v>
+        <v>1.342374198614608</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6920,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.093981</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.317848</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.324343</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.18794</v>
       </c>
     </row>
     <row r="111">
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000428</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001267</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6975,13 +6975,13 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.415529</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.19633</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.036903</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000428</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001267</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8351,13 +8351,13 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.415529</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.19633</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.036903</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -8373,10 +8373,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.731569</v>
+        <v>-0.731997</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.440592</v>
+        <v>-0.441859</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -8413,13 +8413,13 @@
         <v>-1.745052</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-5.792269</v>
+        <v>-6.207798</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-10.095788</v>
+        <v>-10.292118</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-16.701039</v>
+        <v>-16.737942</v>
       </c>
       <c r="Q135" s="3" t="n">
         <v>-7.083461</v>
@@ -25912,7 +25912,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -32024,7 +32028,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -34335,7 +34343,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -34434,7 +34446,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -35036,7 +35052,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -37256,7 +37276,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -37959,7 +37983,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -45308,7 +45336,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -46738,7 +46770,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E383" t="inlineStr">
         <is>
           <t>-</t>
@@ -47241,7 +47277,11 @@
           <t>Shares issued for cash , net (note 10 (b))</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47649,7 +47689,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -52596,7 +52640,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E441" s="5" t="n">
         <v>-0.000428</v>
       </c>
@@ -62698,7 +62746,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -64290,7 +64342,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -70963,7 +71019,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E624" t="inlineStr">
         <is>
           <t>-</t>
@@ -71874,7 +71934,11 @@
           <t>Deferred income tax recovery (note 17)</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr"/>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E633" t="inlineStr">
         <is>
           <t>-</t>
@@ -73084,7 +73148,11 @@
           <t>Deferred income tax recovery (note 22)</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr"/>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E645" t="inlineStr">
         <is>
           <t>-</t>
@@ -74306,7 +74374,11 @@
           <t>Deferred income tax recovery (note 18)</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E657" t="inlineStr">
         <is>
           <t>-</t>
@@ -76645,7 +76717,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E680" s="5" t="n">
         <v>0.837</v>
       </c>
